--- a/PaCTEA_for_study_case/waste_characterization_FR.xlsx
+++ b/PaCTEA_for_study_case/waste_characterization_FR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\biowaste_optim\PaCTEA_for_study_case\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B078F87C-5118-405B-8D3B-4519B03AF3B2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1431258-B433-4E15-A9CD-9022493C1032}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930" activeTab="3" xr2:uid="{14B8D0C9-091E-43B5-9C59-8A05020574F1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930" activeTab="2" xr2:uid="{14B8D0C9-091E-43B5-9C59-8A05020574F1}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="12" r:id="rId1"/>
